--- a/pipeline/PNS_preprocessing_registry_v1.xlsx
+++ b/pipeline/PNS_preprocessing_registry_v1.xlsx
@@ -3812,7 +3812,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7670,6 +7670,21 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Diagnosis gates</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dx_diabetes and dx_cholesterol carried na_rule = implied:0, so an unanswered gate was filled with zero and the row declared undiagnosed. That is bug 1 of the 15/09/2026 build note and it builds 7,851 and 7,244 rows. Set to mar on 22/09/2026, matching dx_hypertension: the cohorts are now 6,832 (3.8%) and 5,944 (32.0%), as reported.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pipeline/PNS_preprocessing_registry_v1.xlsx
+++ b/pipeline/PNS_preprocessing_registry_v1.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:P93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1281,81 +1281,86 @@
       <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A_medication</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>n_medications</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>SUM(block A binaries)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Number of medication classes in use (polypharmacy proxy)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>med_diabetes_insulin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q03402</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Currently uses insulin</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>bin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1 yes, 2 no; not asked of people never told they had diabetes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>implied:0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>B_sociodem</t>
+          <t>A_medication</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>n_medications</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Z002</t>
+          <t>SUM(block A binaries)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Age (years)</t>
+          <t>Number of medication classes in use (polypharmacy proxy)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1365,19 +1370,19 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>spline (5 knots) -&gt; scale</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -1400,28 +1405,28 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>bolsa_familia</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>Z002</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Household receives Bolsa Familia (low-SES marker)</t>
+          <t>Age (years)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1433,7 +1438,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>spline (5 knots) -&gt; scale</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1456,40 +1461,32 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>bolsa_familia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>VDD004</t>
+          <t>F012</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Highest educational level (1-7)</t>
+          <t>Household receives Bolsa Familia (low-SES marker)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1 no instruction -&gt; 7 bachelor's</t>
-        </is>
-      </c>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>mar</t>
@@ -1497,7 +1494,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1520,32 +1517,40 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>VDD004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Number of people in the household</t>
+          <t>Highest educational level (1-7)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1 no instruction -&gt; 7 bachelor's</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>mar</t>
@@ -1553,7 +1558,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1576,28 +1581,28 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>lives_w_partner</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>C010</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Lives with a partner</t>
+          <t>Number of people in the household</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1632,35 +1637,35 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>lives_w_partner</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>log1p(income)</t>
+          <t>C010</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Log of income (income is right-skewed)</t>
+          <t>Lives with a partner</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1688,44 +1693,40 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>log_income</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>C011</t>
+          <t>log1p(income)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Marital status</t>
+          <t>Log of income (income is right-skewed)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5 levels, no collapse needed</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>one-hot, declared levels</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1748,18 +1749,18 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>race</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Z003</t>
+          <t>C011</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Race/skin colour (9=unknown -&gt; NaN)</t>
+          <t>Marital status</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1775,7 +1776,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Collapse by hand BEFORE encoding: 1 white, 2 black, 4 brown, 3+5 other. Code 9 -&gt; NaN. Do NOT rely on min_frequency.</t>
+          <t>5 levels, no collapse needed</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1808,18 +1809,18 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>race</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>regiao</t>
+          <t>Z003</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Region (1 N, 2 NE, 3 SE, 4 S, 5 CW)</t>
+          <t>Race/skin colour (9=unknown -&gt; NaN)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1835,7 +1836,7 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5 macro-regions</t>
+          <t>Collapse by hand BEFORE encoding: 1 white, 2 black, 4 brown, 3+5 other. Code 9 -&gt; NaN. Do NOT rely on min_frequency.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1868,18 +1869,18 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Z001</t>
+          <t>regiao</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sex (1 male, 2 female)</t>
+          <t>Region (1 N, 2 NE, 3 SE, 4 S, 5 CW)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1895,7 +1896,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Registry name is sex (Z001). The exported map carried 'Fri', a generator corruption.</t>
+          <t>5 macro-regions</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1928,18 +1929,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>workforce_status</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VDE001</t>
+          <t>Z001</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Labour-force status</t>
+          <t>Sex (1 male, 2 female)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1955,7 +1956,7 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2 levels</t>
+          <t>Registry name is sex (Z001). The exported map carried 'Fri', a generator corruption.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1983,45 +1984,49 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>C_lifestyle</t>
+          <t>B_sociodem</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>active_commute</t>
+          <t>workforce_status</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>P040</t>
+          <t>VDE001</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Walks/cycles to work</t>
+          <t>Labour-force status</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>nominal</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2 levels</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>one-hot, declared levels</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2044,28 +2049,28 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>alcohol_drinks_week</t>
+          <t>active_commute</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>alcohol_days * alcohol_doses</t>
+          <t>P040</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Quantity-frequency product, standard alcohol exposure</t>
+          <t>Walks/cycles to work</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -2100,48 +2105,40 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>alcohol_freq</t>
+          <t>alcohol_drinks_week</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>alcohol_days * alcohol_doses</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Alcohol consumption frequency</t>
+          <t>Quantity-frequency product, standard alcohol exposure</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1,2,3</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1 never -&gt; 3 once or more per month</t>
-        </is>
-      </c>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2164,40 +2161,48 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>binge_drink</t>
+          <t>alcohol_freq</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>P032</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Binge drinking in the last 30 days</t>
+          <t>Alcohol consumption frequency</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1 never -&gt; 3 once or more per month</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2220,28 +2225,28 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>diet_beans</t>
+          <t>binge_drink</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P032</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating beans</t>
+          <t>Binge drinking in the last 30 days</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -2276,18 +2281,18 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>diet_chicken</t>
+          <t>diet_beans</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating chicken</t>
+          <t>Days/week eating beans</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2332,18 +2337,18 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>diet_cooked_veg</t>
+          <t>diet_chicken</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating cooked vegetables</t>
+          <t>Days/week eating chicken</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2388,18 +2393,18 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>diet_fastfood</t>
+          <t>diet_cooked_veg</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Days/week replacing a meal with fast food</t>
+          <t>Days/week eating cooked vegetables</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2444,18 +2449,18 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>diet_fish</t>
+          <t>diet_fastfood</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating fish</t>
+          <t>Days/week replacing a meal with fast food</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2500,18 +2505,18 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>diet_fruit</t>
+          <t>diet_fish</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating fruit</t>
+          <t>Days/week eating fish</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2556,18 +2561,18 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>diet_juice</t>
+          <t>diet_fruit</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Days/week drinking natural fruit juice</t>
+          <t>Days/week eating fruit</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2612,18 +2617,18 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>diet_milk</t>
+          <t>diet_juice</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>P023</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Days/week drinking milk</t>
+          <t>Days/week drinking natural fruit juice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2668,18 +2673,18 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>diet_red_meat</t>
+          <t>diet_milk</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating red meat</t>
+          <t>Days/week drinking milk</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2724,18 +2729,18 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>diet_salad</t>
+          <t>diet_red_meat</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating raw salad</t>
+          <t>Days/week eating red meat</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2780,52 +2785,40 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>diet_salt_perception</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>salt_perception</t>
-        </is>
-      </c>
+          <t>diet_salad</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>P02601</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Self-perceived salt intake (1 very high - 5 very low)</t>
+          <t>Days/week eating raw salad</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>5,4,3,2,1</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>REVERSED: 5 very low -&gt; 1 very high, so high = more salt</t>
-        </is>
-      </c>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -2848,40 +2841,52 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>diet_soda</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>diet_salt_perception</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>salt_perception</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P02601</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Days/week drinking soda</t>
+          <t>Self-perceived salt intake (1 very high - 5 very low)</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>5,4,3,2,1</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>REVERSED: 5 very low -&gt; 1 very high, so high = more salt</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -2904,18 +2909,18 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>diet_sweets</t>
+          <t>diet_soda</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Days/week eating sweets</t>
+          <t>Days/week drinking soda</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2960,18 +2965,18 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>exercise_days</t>
+          <t>diet_sweets</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>P035</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Days/week of exercise</t>
+          <t>Days/week eating sweets</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3016,18 +3021,18 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>exercise_min_week</t>
+          <t>exercise_days</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>(P03701*60 + P03702) * P035</t>
+          <t>P035</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Total weekly minutes of exercise</t>
+          <t>Days/week of exercise</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3037,7 +3042,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -3072,28 +3077,28 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>heavy_housework</t>
+          <t>exercise_min_week</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>P044</t>
+          <t>(P03701*60 + P03702) * P035</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Heavy housework</t>
+          <t>Total weekly minutes of exercise</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -3128,18 +3133,18 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>heavy_work</t>
+          <t>heavy_housework</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>P039</t>
+          <t>P044</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Heavy physical activity at work</t>
+          <t>Heavy housework</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3184,48 +3189,40 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>passive_smoke</t>
+          <t>heavy_work</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>P068</t>
+          <t>P039</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Frequency of household smoking (passive)</t>
+          <t>Heavy physical activity at work</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>5,4,3,2,1</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>REVERSED: 5 never -&gt; 1 daily, so high = more exposure</t>
-        </is>
-      </c>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3248,40 +3245,48 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>smoke_start_age</t>
+          <t>passive_smoke</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>P053</t>
+          <t>P068</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Age started smoking daily</t>
+          <t>Frequency of household smoking (passive)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>5,4,3,2,1</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>REVERSED: 5 never -&gt; 1 daily, so high = more exposure</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>explicit_na</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>flag + within-responder centred value</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3304,40 +3309,40 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>smoker_past</t>
+          <t>smoke_start_age</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P053</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Ever smoked in the past</t>
+          <t>Age started smoking daily</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>explicit_na</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>flag + within-responder centred value</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3360,52 +3365,40 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>smoking_status</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>smoker_current</t>
-        </is>
-      </c>
+          <t>smoker_past</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>P050</t>
+          <t>P052</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Current tobacco use (1 daily, 2 occasional, 3 no)</t>
+          <t>Ever smoked in the past</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>3,2,1</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>REVERSED: 3 does not smoke -&gt; 1 daily</t>
-        </is>
-      </c>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3428,18 +3421,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>tv_hours</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
+          <t>smoking_status</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>smoker_current</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>P045</t>
+          <t>P050</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Hours/day watching TV (8 = does not watch)</t>
+          <t>Current tobacco use (1 daily, 2 occasional, 3 no)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3454,12 +3451,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,1,2,3,4,5,6,7</t>
+          <t>3,2,1</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>RECODED: source code 8 ('does not watch') -&gt; 0</t>
+          <t>REVERSED: 3 does not smoke -&gt; 1 daily</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3492,40 +3489,48 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>walks_at_work</t>
+          <t>tv_hours</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>P038</t>
+          <t>P045</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Walks a lot at work</t>
+          <t>Hours/day watching TV (8 = does not watch)</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0,1,2,3,4,5,6,7</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>RECODED: source code 8 ('does not watch') -&gt; 0</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -3543,40 +3548,40 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>D_health</t>
+          <t>C_lifestyle</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>bmi</t>
+          <t>walks_at_work</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>weight_kg/(height_cm/100)^2</t>
+          <t>P038</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Body Mass Index</t>
+          <t>Walks a lot at work</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3585,13 +3590,13 @@
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
@@ -3604,36 +3609,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>chest_pain_exertion</t>
+          <t>bmi</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>weight_kg/(height_cm/100)^2</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Chest pain when climbing/walking fast</t>
+          <t>Body Mass Index</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>check level frequencies before encoding</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
           <t>mar</t>
@@ -3641,17 +3642,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>one-hot, declared levels</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
@@ -3664,40 +3665,44 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>dx_arthritis</t>
+          <t>chest_pain_exertion</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Q079</t>
+          <t>N004</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with arthritis</t>
+          <t>Chest pain when climbing/walking fast</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>nominal</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>check level frequencies before encoding</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>one-hot, declared levels</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -3710,11 +3715,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="P53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3724,18 +3725,18 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>dx_asthma</t>
+          <t>dx_arthritis</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Q074</t>
+          <t>Q079</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with asthma</t>
+          <t>Ever diagnosed with arthritis</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3784,18 +3785,18 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>dx_cholesterol</t>
+          <t>dx_asthma</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Q060</t>
+          <t>Q074</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with high cholesterol</t>
+          <t>Ever diagnosed with asthma</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3812,7 +3813,7 @@
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3827,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr">
@@ -3844,18 +3845,18 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>dx_depression</t>
+          <t>dx_cholesterol</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Q092</t>
+          <t>Q060</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with depression</t>
+          <t>Ever diagnosed with high cholesterol</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3872,7 +3873,7 @@
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3887,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
@@ -3904,18 +3905,18 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>dx_diabetes</t>
+          <t>dx_depression</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q092</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with diabetes</t>
+          <t>Ever diagnosed with depression</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3932,7 +3933,7 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3944,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" s="2" t="n">
         <v>0</v>
@@ -3964,18 +3965,18 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>dx_heart</t>
+          <t>dx_diabetes</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Q063</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with heart disease</t>
+          <t>Ever diagnosed with diabetes</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3992,7 +3993,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4004,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" s="2" t="n">
         <v>0</v>
@@ -4024,18 +4025,18 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>dx_hypertension</t>
+          <t>dx_heart</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q063</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with hypertension</t>
+          <t>Ever diagnosed with heart disease</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4052,7 +4053,7 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4061,7 +4062,7 @@
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>0</v>
@@ -4084,18 +4085,18 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>dx_kidney</t>
+          <t>dx_hypertension</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Q124</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with chronic kidney disease</t>
+          <t>Ever diagnosed with hypertension</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4112,7 +4113,7 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4121,7 +4122,7 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>0</v>
@@ -4144,18 +4145,18 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>dx_lung</t>
+          <t>dx_kidney</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Q116</t>
+          <t>Q124</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with lung disease/COPD</t>
+          <t>Ever diagnosed with chronic kidney disease</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4204,18 +4205,18 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>dx_other_chronic</t>
+          <t>dx_lung</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Q128</t>
+          <t>Q116</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Any other chronic disease diagnosis</t>
+          <t>Ever diagnosed with lung disease/COPD</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4264,18 +4265,18 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>dx_spine</t>
+          <t>dx_other_chronic</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Q084</t>
+          <t>Q128</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Chronic spinal problem</t>
+          <t>Any other chronic disease diagnosis</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4324,18 +4325,18 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>dx_stroke</t>
+          <t>dx_spine</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Q068</t>
+          <t>Q084</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Ever diagnosed with stroke</t>
+          <t>Chronic spinal problem</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4384,22 +4385,18 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>dx_wrmd</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>dx_dort</t>
-        </is>
-      </c>
+          <t>dx_stroke</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Q088</t>
+          <t>Q068</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Work-related musculoskeletal disorder</t>
+          <t>Ever diagnosed with stroke</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4448,48 +4445,44 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>mobility_difficulty</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
+          <t>dx_wrmd</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>dx_dort</t>
+        </is>
+      </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>Q088</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Difficulty walking</t>
+          <t>Work-related musculoskeletal disorder</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>1 none -&gt; 5 cannot</t>
-        </is>
-      </c>
+          <t>yes_no</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -4502,7 +4495,11 @@
         <v>0</v>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4512,40 +4509,48 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>n_chronic</t>
+          <t>mobility_difficulty</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>SUM(dx_* except hypertension)</t>
+          <t>N003</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Comorbidity count</t>
+          <t>Difficulty walking</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>1 none -&gt; 5 cannot</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>implied:0</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -4568,48 +4573,40 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>self_rated_health</t>
+          <t>n_chronic</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>N001</t>
+          <t>SUM(dx_* except hypertension)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Self-rated health (1 very good - 5 very poor)</t>
+          <t>Comorbidity count</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>1 very good -&gt; 5 very bad</t>
-        </is>
-      </c>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>implied:0</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -4632,32 +4629,40 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>waist_cm</t>
+          <t>self_rated_health</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>W00303</t>
+          <t>N001</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Measured waist circumference (cm)</t>
+          <t>Self-rated health (1 very good - 5 very poor)</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>1 very good -&gt; 5 very bad</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
           <t>mar</t>
@@ -4665,17 +4670,17 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
       <c r="P69" s="2" t="inlineStr"/>
@@ -4683,55 +4688,55 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>E_access</t>
+          <t>D_health</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>care_same_city</t>
+          <t>waist_cm</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>X008</t>
+          <t>W00303</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Care located in the same city of residence</t>
+          <t>Measured waist circumference (cm)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>explicit_na</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>one-hot (3 levels incl. NA_nao_aplicavel)</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr"/>
@@ -4744,18 +4749,18 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>consult_by_plan</t>
+          <t>care_same_city</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>X017</t>
+          <t>X008</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Consultation covered by insurance</t>
+          <t>Care located in the same city of residence</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4800,28 +4805,28 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>consult_minutes</t>
+          <t>consult_by_plan</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>X01501*60 + X01502</t>
+          <t>X017</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Duration of the consultation (minutes)</t>
+          <t>Consultation covered by insurance</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4833,7 +4838,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>flag + within-responder centred value</t>
+          <t>one-hot (3 levels incl. NA_nao_aplicavel)</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -4856,28 +4861,28 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>consult_paid</t>
+          <t>consult_minutes</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>X018</t>
+          <t>X01501*60 + X01502</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Paid out of pocket for the consultation</t>
+          <t>Duration of the consultation (minutes)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4889,7 +4894,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>one-hot (3 levels incl. NA_nao_aplicavel)</t>
+          <t>flag + within-responder centred value</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -4912,36 +4917,32 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>consult_sus</t>
+          <t>consult_paid</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>X019</t>
+          <t>X018</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Consultation through SUS (public system)</t>
+          <t>Paid out of pocket for the consultation</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>4 levels + NA_nao_aplicavel</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
           <t>explicit_na</t>
@@ -4949,7 +4950,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>one-hot, declared levels</t>
+          <t>one-hot (3 levels incl. NA_nao_aplicavel)</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -4972,18 +4973,18 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>doctor_type</t>
+          <t>consult_sus</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>X016</t>
+          <t>X019</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Type of doctor seen</t>
+          <t>Consultation through SUS (public system)</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4999,7 +5000,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>6 levels + NA_nao_aplicavel</t>
+          <t>4 levels + NA_nao_aplicavel</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -5032,18 +5033,18 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>first_care_place</t>
+          <t>doctor_type</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>X003</t>
+          <t>X016</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Where first care was sought (13 categories)</t>
+          <t>Type of doctor seen</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -5059,7 +5060,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14 levels + NA_nao_aplicavel, declare the collapse</t>
+          <t>6 levels + NA_nao_aplicavel</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5092,32 +5093,36 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>got_care_first_try</t>
+          <t>first_care_place</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>X004</t>
+          <t>X003</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Obtained care on the first attempt</t>
+          <t>Where first care was sought (13 categories)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>nominal</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>14 levels + NA_nao_aplicavel, declare the collapse</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
           <t>explicit_na</t>
@@ -5125,7 +5130,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>one-hot (3 levels incl. NA_nao_aplicavel)</t>
+          <t>one-hot, declared levels</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -5148,18 +5153,18 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>health_insurance</t>
+          <t>got_care_first_try</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>I001</t>
+          <t>X004</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Has private health insurance</t>
+          <t>Obtained care on the first attempt</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5176,12 +5181,12 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>explicit_na</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>one-hot (3 levels incl. NA_nao_aplicavel)</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -5204,18 +5209,18 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>hospitalized_12m</t>
+          <t>health_insurance</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>J037</t>
+          <t>I001</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Hospitalised &gt;=24h in the last 12 months</t>
+          <t>Has private health insurance</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -5260,44 +5265,40 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>how_got_appt</t>
+          <t>hospitalized_12m</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>X011</t>
+          <t>J037</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>How the appointment was obtained</t>
+          <t>Hospitalised &gt;=24h in the last 12 months</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>9 levels + NA_nao_aplicavel</t>
-        </is>
-      </c>
+      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>explicit_na</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>one-hot, declared levels</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -5320,18 +5321,18 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>last_bp_measure</t>
+          <t>how_got_appt</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>X011</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Time since BP was last measured</t>
+          <t>How the appointment was obtained</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -5341,31 +5342,27 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6</t>
-        </is>
-      </c>
+          <t>nominal</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>1 &lt;6 months -&gt; 6 never</t>
+          <t>9 levels + NA_nao_aplicavel</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>explicit_na</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>one-hot, declared levels</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>0</v>
@@ -5384,18 +5381,18 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>last_glucose_test</t>
+          <t>last_bp_measure</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Time since last blood glucose test</t>
+          <t>Time since BP was last measured</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5432,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>0</v>
@@ -5448,18 +5445,18 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>last_medical_visit</t>
+          <t>last_glucose_test</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>X001</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Time since last medical consultation (1 &lt;2wk - 6 never)</t>
+          <t>Time since last blood glucose test</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5479,7 +5476,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>1 &lt;2 weeks -&gt; 6 never</t>
+          <t>1 &lt;6 months -&gt; 6 never</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5512,32 +5509,40 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>n_discrimination</t>
+          <t>last_medical_visit</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>SUM(X02501..X02510)</t>
+          <t>X001</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Number of discrimination settings reported</t>
+          <t>Time since last medical consultation (1 &lt;2wk - 6 never)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>1 &lt;2 weeks -&gt; 6 never</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
           <t>mar</t>
@@ -5545,7 +5550,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>ordinal encoder, declared order</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -5568,32 +5573,28 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>public_space_nearby</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>public_space</t>
-        </is>
-      </c>
+          <t>n_discrimination</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>P046</t>
+          <t>SUM(X02501..X02510)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Public space for exercise near home</t>
+          <t>Number of discrimination settings reported</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -5628,44 +5629,44 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>qual_index</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr"/>
+          <t>public_space_nearby</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>public_space</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>MEAN(X02001,X02004,X02201,X02203)</t>
+          <t>P046</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Mean of four service-quality ratings, complete raters only</t>
+          <t>Public space for exercise near home</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>mean of four 5-point ratings, 1 very good -&gt; 5 very bad</t>
-        </is>
-      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>explicit_na</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>flag + within-responder centred value</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -5688,40 +5689,44 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>restricted_activity_2w</t>
+          <t>qual_index</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>J002</t>
+          <t>MEAN(X02001,X02004,X02201,X02203)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Stopped usual activities for health reasons (2 wk)</t>
+          <t>Mean of four service-quality ratings, complete raters only</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>bin</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>yes_no</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>mean of four 5-point ratings, 1 very good -&gt; 5 very bad</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>explicit_na</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>numeric: median impute (+indicator) -&gt; scale</t>
+          <t>flag + within-responder centred value</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -5744,18 +5749,18 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>sought_care_2w</t>
+          <t>restricted_activity_2w</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>J014</t>
+          <t>J002</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Sought health care in the last 2 weeks</t>
+          <t>Stopped usual activities for health reasons (2 wk)</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5800,44 +5805,40 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>visit_reason</t>
+          <t>sought_care_2w</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>X002</t>
+          <t>J014</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Reason for the last consultation</t>
+          <t>Sought health care in the last 2 weeks</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>bin</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>yes_no</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>9 levels + NA_nao_aplicavel</t>
-        </is>
-      </c>
+      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>explicit_na</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>one-hot, declared levels</t>
+          <t>numeric: median impute (+indicator) -&gt; scale</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -5860,32 +5861,36 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>wait_minutes</t>
+          <t>visit_reason</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>X01401*60 + X01402</t>
+          <t>X002</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Waiting time in the queue (minutes)</t>
+          <t>Reason for the last consultation</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>num</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>nominal</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>9 levels + NA_nao_aplicavel</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>explicit_na</t>
@@ -5893,7 +5898,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>flag + within-responder centred value</t>
+          <t>one-hot, declared levels</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -5911,53 +5916,45 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>F_sleep</t>
+          <t>E_access</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>sleep_problems</t>
+          <t>wait_minutes</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>X01401*60 + X01402</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Frequency of sleep problems, last 2 weeks (1 none - 4 almost daily)</t>
+          <t>Waiting time in the queue (minutes)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>num</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>1,2,3,4</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>1 no day -&gt; 4 almost every day</t>
-        </is>
-      </c>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>explicit_na</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>ordinal encoder, declared order</t>
+          <t>flag + within-responder centred value</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
@@ -5980,18 +5977,18 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>unrested</t>
+          <t>sleep_problems</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N010</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Frequency of feeling unrested, last 2 weeks</t>
+          <t>Frequency of sleep problems, last 2 weeks (1 none - 4 almost daily)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -6035,6 +6032,70 @@
       </c>
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>F_sleep</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>unrested</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>N011</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Frequency of feeling unrested, last 2 weeks</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>1 no day -&gt; 4 almost every day</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>ordinal encoder, declared order</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P92"/>
@@ -6955,16 +7016,16 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Q002 (1 yes, 2 pregnancy-only -&gt; yes, 3 no)</t>
+          <t>Q002 (1 yes, 2 pregnancy-only -&gt; undefined, drops, 3 no)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8855</v>
+        <v>8830</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6972,7 +7033,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6346</v>
+        <v>6329</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -6986,7 +7047,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>dx_hypertension, med_hypertension_2w, last_bp_measure</t>
+          <t>dx_hypertension, med_hypertension_2w</t>
         </is>
       </c>
     </row>
@@ -7013,16 +7074,16 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Q030 (2 pregnancy-only -&gt; yes, per Q002)</t>
+          <t>Q030 (1 yes, 2 pregnancy-only -&gt; undefined, drops, 3 no)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8459</v>
+        <v>8435</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -7030,7 +7091,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6832</v>
+        <v>6812</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -7044,7 +7105,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>dx_diabetes, med_diabetes_2w, last_glucose_test, Q031</t>
+          <t>dx_diabetes, med_diabetes_insulin</t>
         </is>
       </c>
     </row>
@@ -7076,11 +7137,11 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8448</v>
+        <v>8425</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7088,11 +7149,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5944</v>
+        <v>5927</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -7102,7 +7163,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>dx_cholesterol, Q061, Q06201-Q06206</t>
+          <t>dx_cholesterol</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7441,7 +7502,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Dropped as condition-specific for the hypertension model, per the generated map and Xuan's sheet. Task 4 asks for it back. Open with the team. If it returns, last_glucose_test must return symmetrically for the diabetes model.</t>
+          <t>DECIDED 22/09/2026. Returns as a predictor for the blood pressure model, and last_glucose_test returns for diabetes, symmetrically. Both are health-service contact items, not examination results. Read their coefficients with the caveat that treated people are often controlled at measurement, so contact can carry an inverted association. Registry: leak_hypertension and leak_diabetes set to 0.</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7517,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>'Only during pregnancy' coded as diagnosed, matching the Q002 treatment. Alternative reading is that a past gestational episode is a risk factor, not current diabetes. Revisit if diabetes becomes primary.</t>
+          <t>DECIDED 22/09/2026. Gestational diabetes is a distinct condition, so 'only during pregnancy' no longer counts as diagnosed: the gate is undefined and the row leaves the base, counted in the attrition file. Q002 = 2 treated the same way for blood pressure. 35 and 144 rows respectively. The undiagnosed cohorts are unaffected, since those rows were already outside them.</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7547,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Absent from the registry. Needs adding to block A, and excluding from n_medications for the diabetes model.</t>
+          <t>DECIDED 22/09/2026. Declared in block A as med_diabetes_insulin, na_rule implied:0 (97 users, 505 no, the rest a skip pattern). leak_diabetes = 1, so it leaves the diabetes model and, by the counter-rebuilding rule, leaves n_medications there as well. It stays a predictor for blood pressure and cholesterol.</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7562,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PNS 2013 has no such item. Q06204 records a recommendation, not use. The cholesterol model cannot define 'treated' the way the other two can.</t>
+          <t>DECIDED 22/09/2026. Recorded as a limitation in 05_article/Methods.docx. No treated or untreated subgroup analysis is reported for cholesterol. Q06204 records a recommendation, not use.</t>
         </is>
       </c>
     </row>
@@ -7682,6 +7743,36 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>dx_diabetes and dx_cholesterol carried na_rule = implied:0, so an unanswered gate was filled with zero and the row declared undiagnosed. That is bug 1 of the 15/09/2026 build note and it builds 7,851 and 7,244 rows. Set to mar on 22/09/2026, matching dx_hypertension: the cohorts are now 6,832 (3.8%) and 5,944 (32.0%), as reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pregnancy exclusion</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DECIDED 22/09/2026. P005 = 1 (pregnant, 89) and P005 = 3 (does not know, 25) both leave the base: an undefined pregnancy is not a known non-pregnancy. 114 rows in all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Condition-specific source</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The list of condition-specific columns is read from the leak_&lt;outcome&gt; columns of this sheet instead of a list written in pns_preprocess.py. The script no longer carries a variable decision, and it no longer names med_diabetes_2w, which is in the dropped sheet.</t>
         </is>
       </c>
     </row>
